--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -708,11 +708,10 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
@@ -773,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32870-2020 artfynd.xlsx
+++ b/artfynd/A 32870-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122527879</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
